--- a/satisfaction_surveys/009_private_jet_grooming_feedback_form--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/009_private_jet_grooming_feedback_form--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please share your experience with our private jet grooming service.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CleanlinessRatings</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Cleanliness Ratings</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the cleanliness of our private jet.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,46 +569,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cleanliness_ratings_2</t>
+          <t>cleanliness_score</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CleanlinessRatings2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Cleanliness Score</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate the cleanliness of our private jet on a scale of 1-10.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>grooming_services</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GroomingServices</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter your email address for us to contact you.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cleanliness_score</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CleanlinessScore</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Share your thoughts about our service.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter your name for verification purposes.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>confirm_cleanliness_ratings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Confirm Cleanliness Ratings</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Confirm your cleanliness ratings above.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments_2</t>
+          <t>confirm_cleanliness_score</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Confirm Cleanliness Score</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Confirm the cleanliness score you provided above.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Share any additional comments or concerns.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>submit_button</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Complete the feedback form.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>final_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Final Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Leave any final comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments_3</t>
+          <t>repeat_name_and_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Confirm Your Information</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Confirm your name and email address.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>comments_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>comments_5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>comments_6</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>comments_7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>comments_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>comments_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments_12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments_13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments_14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments_15</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments_16</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +847,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +909,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cleanliness_ratings_2_choices</t>
+          <t>confirm_cleanliness_ratings_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +926,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cleanliness_ratings_2_choices</t>
+          <t>confirm_cleanliness_ratings_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1188,40 +937,6 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>grooming_services_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>grooming_services_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
